--- a/artfynd/A 29942-2020 artfynd.xlsx
+++ b/artfynd/A 29942-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 29942-2020 artfynd.xlsx
+++ b/artfynd/A 29942-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1498,6 +1498,135 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122162356</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98140</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Holsbybrunn, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>511528</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6366102</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-01-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-01-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>20-25tal plantor</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Birgitta Svensson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Birgitta Svensson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29942-2020 artfynd.xlsx
+++ b/artfynd/A 29942-2020 artfynd.xlsx
@@ -1503,7 +1503,7 @@
         <v>122162356</v>
       </c>
       <c r="B9" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 29942-2020 artfynd.xlsx
+++ b/artfynd/A 29942-2020 artfynd.xlsx
@@ -1503,7 +1503,7 @@
         <v>122162356</v>
       </c>
       <c r="B9" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>122273417</v>
       </c>
       <c r="B10" t="n">
-        <v>97129</v>
+        <v>97139</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 29942-2020 artfynd.xlsx
+++ b/artfynd/A 29942-2020 artfynd.xlsx
@@ -1503,7 +1503,7 @@
         <v>122162356</v>
       </c>
       <c r="B9" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>122273417</v>
       </c>
       <c r="B10" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 29942-2020 artfynd.xlsx
+++ b/artfynd/A 29942-2020 artfynd.xlsx
@@ -1503,7 +1503,7 @@
         <v>122162356</v>
       </c>
       <c r="B9" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>122273417</v>
       </c>
       <c r="B10" t="n">
-        <v>97151</v>
+        <v>97156</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 29942-2020 artfynd.xlsx
+++ b/artfynd/A 29942-2020 artfynd.xlsx
@@ -1503,7 +1503,7 @@
         <v>122162356</v>
       </c>
       <c r="B9" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1517,11 +1517,6 @@
       </c>
       <c r="E9" t="n">
         <v>220787</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1632,7 +1627,7 @@
         <v>122273417</v>
       </c>
       <c r="B10" t="n">
-        <v>97156</v>
+        <v>97165</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1646,11 +1641,6 @@
       </c>
       <c r="E10" t="n">
         <v>221945</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>

--- a/artfynd/A 29942-2020 artfynd.xlsx
+++ b/artfynd/A 29942-2020 artfynd.xlsx
@@ -1503,7 +1503,7 @@
         <v>122162356</v>
       </c>
       <c r="B9" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1517,6 +1517,11 @@
       </c>
       <c r="E9" t="n">
         <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -1627,7 +1632,7 @@
         <v>122273417</v>
       </c>
       <c r="B10" t="n">
-        <v>97165</v>
+        <v>97178</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1641,6 +1646,11 @@
       </c>
       <c r="E10" t="n">
         <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>

--- a/artfynd/A 29942-2020 artfynd.xlsx
+++ b/artfynd/A 29942-2020 artfynd.xlsx
@@ -1503,7 +1503,7 @@
         <v>122162356</v>
       </c>
       <c r="B9" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>122273417</v>
       </c>
       <c r="B10" t="n">
-        <v>97178</v>
+        <v>97191</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 29942-2020 artfynd.xlsx
+++ b/artfynd/A 29942-2020 artfynd.xlsx
@@ -1632,7 +1632,7 @@
         <v>122273417</v>
       </c>
       <c r="B10" t="n">
-        <v>97191</v>
+        <v>97194</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 29942-2020 artfynd.xlsx
+++ b/artfynd/A 29942-2020 artfynd.xlsx
@@ -1632,7 +1632,7 @@
         <v>122273417</v>
       </c>
       <c r="B10" t="n">
-        <v>97194</v>
+        <v>97195</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 29942-2020 artfynd.xlsx
+++ b/artfynd/A 29942-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1739,6 +1739,230 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122706725</v>
+      </c>
+      <c r="B11" t="n">
+        <v>105350</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Holsbybrunn, Holsbybrunn, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>511483</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6366108</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Birgitta Svensson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Birgitta Svensson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122706750</v>
+      </c>
+      <c r="B12" t="n">
+        <v>105350</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Holsbybrunn, Holsbybrunn, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>511386</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6366167</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Birgitta Svensson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Birgitta Svensson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29942-2020 artfynd.xlsx
+++ b/artfynd/A 29942-2020 artfynd.xlsx
@@ -1744,7 +1744,7 @@
         <v>122706725</v>
       </c>
       <c r="B11" t="n">
-        <v>105350</v>
+        <v>105453</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         <v>122706750</v>
       </c>
       <c r="B12" t="n">
-        <v>105350</v>
+        <v>105453</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 29942-2020 artfynd.xlsx
+++ b/artfynd/A 29942-2020 artfynd.xlsx
@@ -1741,10 +1741,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122706725</v>
+        <v>122706750</v>
       </c>
       <c r="B11" t="n">
-        <v>105453</v>
+        <v>105461</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511483</v>
+        <v>511386</v>
       </c>
       <c r="R11" t="n">
-        <v>6366108</v>
+        <v>6366167</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1853,10 +1853,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122706750</v>
+        <v>122706725</v>
       </c>
       <c r="B12" t="n">
-        <v>105453</v>
+        <v>105461</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511386</v>
+        <v>511483</v>
       </c>
       <c r="R12" t="n">
-        <v>6366167</v>
+        <v>6366108</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 29942-2020 artfynd.xlsx
+++ b/artfynd/A 29942-2020 artfynd.xlsx
@@ -1741,7 +1741,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122706750</v>
+        <v>122706725</v>
       </c>
       <c r="B11" t="n">
         <v>105461</v>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511386</v>
+        <v>511483</v>
       </c>
       <c r="R11" t="n">
-        <v>6366167</v>
+        <v>6366108</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1853,7 +1853,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122706725</v>
+        <v>122706750</v>
       </c>
       <c r="B12" t="n">
         <v>105461</v>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511483</v>
+        <v>511386</v>
       </c>
       <c r="R12" t="n">
-        <v>6366108</v>
+        <v>6366167</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 29942-2020 artfynd.xlsx
+++ b/artfynd/A 29942-2020 artfynd.xlsx
@@ -1741,10 +1741,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122706725</v>
+        <v>122706750</v>
       </c>
       <c r="B11" t="n">
-        <v>105461</v>
+        <v>105463</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511483</v>
+        <v>511386</v>
       </c>
       <c r="R11" t="n">
-        <v>6366108</v>
+        <v>6366167</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1853,10 +1853,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122706750</v>
+        <v>122706725</v>
       </c>
       <c r="B12" t="n">
-        <v>105461</v>
+        <v>105463</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511386</v>
+        <v>511483</v>
       </c>
       <c r="R12" t="n">
-        <v>6366167</v>
+        <v>6366108</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 29942-2020 artfynd.xlsx
+++ b/artfynd/A 29942-2020 artfynd.xlsx
@@ -1503,7 +1503,7 @@
         <v>122162356</v>
       </c>
       <c r="B9" t="n">
-        <v>98237</v>
+        <v>98357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1611,6 +1611,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 29942-2020 artfynd.xlsx
+++ b/artfynd/A 29942-2020 artfynd.xlsx
@@ -1503,7 +1503,7 @@
         <v>122162356</v>
       </c>
       <c r="B9" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>122706750</v>
       </c>
       <c r="B11" t="n">
-        <v>105463</v>
+        <v>105471</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>122706725</v>
       </c>
       <c r="B12" t="n">
-        <v>105463</v>
+        <v>105471</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 29942-2020 artfynd.xlsx
+++ b/artfynd/A 29942-2020 artfynd.xlsx
@@ -1742,7 +1742,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122706750</v>
+        <v>122706725</v>
       </c>
       <c r="B11" t="n">
         <v>105471</v>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511386</v>
+        <v>511483</v>
       </c>
       <c r="R11" t="n">
-        <v>6366167</v>
+        <v>6366108</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1854,7 +1854,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122706725</v>
+        <v>122706750</v>
       </c>
       <c r="B12" t="n">
         <v>105471</v>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511483</v>
+        <v>511386</v>
       </c>
       <c r="R12" t="n">
-        <v>6366108</v>
+        <v>6366167</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 29942-2020 artfynd.xlsx
+++ b/artfynd/A 29942-2020 artfynd.xlsx
@@ -1742,7 +1742,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122706725</v>
+        <v>122706750</v>
       </c>
       <c r="B11" t="n">
         <v>105471</v>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511483</v>
+        <v>511386</v>
       </c>
       <c r="R11" t="n">
-        <v>6366108</v>
+        <v>6366167</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1854,7 +1854,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122706750</v>
+        <v>122706725</v>
       </c>
       <c r="B12" t="n">
         <v>105471</v>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511386</v>
+        <v>511483</v>
       </c>
       <c r="R12" t="n">
-        <v>6366167</v>
+        <v>6366108</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 29942-2020 artfynd.xlsx
+++ b/artfynd/A 29942-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1964,6 +1964,118 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123411380</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98368</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Holsbybrunn, Holsbybrunn, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>511450</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6366105</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Alseda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Birgitta Svensson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Birgitta Svensson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29942-2020 artfynd.xlsx
+++ b/artfynd/A 29942-2020 artfynd.xlsx
@@ -1503,7 +1503,7 @@
         <v>122162356</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 29942-2020 artfynd.xlsx
+++ b/artfynd/A 29942-2020 artfynd.xlsx
@@ -1503,7 +1503,7 @@
         <v>122162356</v>
       </c>
       <c r="B9" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>123411380</v>
       </c>
       <c r="B13" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 29942-2020 artfynd.xlsx
+++ b/artfynd/A 29942-2020 artfynd.xlsx
@@ -1503,7 +1503,7 @@
         <v>122162356</v>
       </c>
       <c r="B9" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>123411380</v>
       </c>
       <c r="B13" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 29942-2020 artfynd.xlsx
+++ b/artfynd/A 29942-2020 artfynd.xlsx
@@ -1503,7 +1503,7 @@
         <v>122162356</v>
       </c>
       <c r="B9" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>123411380</v>
       </c>
       <c r="B13" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 29942-2020 artfynd.xlsx
+++ b/artfynd/A 29942-2020 artfynd.xlsx
@@ -1503,7 +1503,7 @@
         <v>122162356</v>
       </c>
       <c r="B9" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>123411380</v>
       </c>
       <c r="B13" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 29942-2020 artfynd.xlsx
+++ b/artfynd/A 29942-2020 artfynd.xlsx
@@ -1503,7 +1503,7 @@
         <v>122162356</v>
       </c>
       <c r="B9" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>123411380</v>
       </c>
       <c r="B13" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 29942-2020 artfynd.xlsx
+++ b/artfynd/A 29942-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1500,10 +1500,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122162356</v>
+        <v>122273417</v>
       </c>
       <c r="B9" t="n">
-        <v>98502</v>
+        <v>97195</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1512,43 +1512,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Holsbybrunn, Sm</t>
+          <t>Holsbybrunn, Holsbybrunn, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1582,27 +1570,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>20-25tal plantor</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,7 +1594,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1630,10 +1612,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122273417</v>
+        <v>122706750</v>
       </c>
       <c r="B10" t="n">
-        <v>97195</v>
+        <v>105471</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1646,21 +1628,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1670,13 +1652,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>511528</v>
+        <v>511386</v>
       </c>
       <c r="R10" t="n">
-        <v>6366102</v>
+        <v>6366167</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1700,22 +1682,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1742,7 +1724,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122706750</v>
+        <v>122706725</v>
       </c>
       <c r="B11" t="n">
         <v>105471</v>
@@ -1782,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>511386</v>
+        <v>511483</v>
       </c>
       <c r="R11" t="n">
-        <v>6366167</v>
+        <v>6366108</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1817,7 +1799,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1827,7 +1809,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1854,10 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122706725</v>
+        <v>123411380</v>
       </c>
       <c r="B12" t="n">
-        <v>105471</v>
+        <v>98504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1866,25 +1848,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1894,10 +1876,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>511483</v>
+        <v>511450</v>
       </c>
       <c r="R12" t="n">
-        <v>6366108</v>
+        <v>6366105</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1924,22 +1906,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1963,118 +1945,6 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>123411380</v>
-      </c>
-      <c r="B13" t="n">
-        <v>98502</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Holsbybrunn, Holsbybrunn, Sm</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>511450</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6366105</v>
-      </c>
-      <c r="S13" t="n">
-        <v>1</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Jönköping</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Vetlanda</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Alseda</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Birgitta Svensson</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Birgitta Svensson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29942-2020 artfynd.xlsx
+++ b/artfynd/A 29942-2020 artfynd.xlsx
@@ -1839,7 +1839,7 @@
         <v>123411380</v>
       </c>
       <c r="B12" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
